--- a/figures_updated/Fig4_stats.xlsx
+++ b/figures_updated/Fig4_stats.xlsx
@@ -404,16 +404,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>0.194</v>
+        <v>0.1931</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0376</v>
+        <v>0.0373</v>
       </c>
       <c r="F2" t="n">
-        <v>0.201563993048928</v>
+        <v>0.193523027287165</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -430,13 +430,13 @@
         <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.398</v>
+        <v>-0.361</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1584</v>
+        <v>0.1303</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00217143518097984</v>
+        <v>0.00580113791612979</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -453,13 +453,13 @@
         <v>57</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7404</v>
+        <v>0.73</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5481</v>
+        <v>0.5328</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0000000000464852600856602</v>
+        <v>0.000000000117578391467532</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -473,16 +473,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4819</v>
+        <v>-0.4816</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2322</v>
+        <v>0.2319</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000802880030856379</v>
+        <v>0.000610142365748967</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -496,16 +496,16 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1461</v>
+        <v>-0.0812</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0213</v>
+        <v>0.0066</v>
       </c>
       <c r="F6" t="n">
-        <v>0.33837102274489</v>
+        <v>0.587590566714176</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.248</v>
+        <v>-0.1766</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0615</v>
+        <v>0.0312</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0629055767810955</v>
+        <v>0.188688558028287</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
